--- a/data/club.xlsx
+++ b/data/club.xlsx
@@ -1,35 +1,143 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
-  <workbookProtection/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\marce\Proyectos\juventud-san-rafael\data\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7504A343-B022-4504-87FD-627F3D8BA15B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Club" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Hitos" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Club" sheetId="1" r:id="rId1"/>
+    <sheet name="Hitos" sheetId="2" r:id="rId2"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="33">
+  <si>
+    <t>nombre</t>
+  </si>
+  <si>
+    <t>apodo</t>
+  </si>
+  <si>
+    <t>fundacion</t>
+  </si>
+  <si>
+    <t>comuna</t>
+  </si>
+  <si>
+    <t>region</t>
+  </si>
+  <si>
+    <t>colores</t>
+  </si>
+  <si>
+    <t>estadio</t>
+  </si>
+  <si>
+    <t>resumen</t>
+  </si>
+  <si>
+    <t>Club Deportivo Juventud San Rafael</t>
+  </si>
+  <si>
+    <t>J con U, La Juve</t>
+  </si>
+  <si>
+    <t>La Pintana</t>
+  </si>
+  <si>
+    <t>Metropolitana</t>
+  </si>
+  <si>
+    <t>Estadio Municipal de La Pintana</t>
+  </si>
+  <si>
+    <t>Fundado por un grupo de vecinos de San Rafael, el club nació como espacio de encuentro y hoy reúne a más de 300 jugadoras y jugadores en sus distintas series, desde Escuela de Fútbol hasta el plantel adulto.</t>
+  </si>
+  <si>
+    <t>anio</t>
+  </si>
+  <si>
+    <t>titulo</t>
+  </si>
+  <si>
+    <t>texto</t>
+  </si>
+  <si>
+    <t>Fundación</t>
+  </si>
+  <si>
+    <t>1978</t>
+  </si>
+  <si>
+    <t>Primer título comunal</t>
+  </si>
+  <si>
+    <t>El primer equipo se corona campeón de la liga vecinal, el primer trofeo que se exhibe en la sede social.</t>
+  </si>
+  <si>
+    <t>1991</t>
+  </si>
+  <si>
+    <t>Construcción de la sede</t>
+  </si>
+  <si>
+    <t>Con trabajo comunitario y aportes de socios se levanta la sede social, que hasta hoy funciona como punto de encuentro de las familias del club.</t>
+  </si>
+  <si>
+    <t>2005</t>
+  </si>
+  <si>
+    <t>Nace la rama femenina</t>
+  </si>
+  <si>
+    <t>Se forma oficialmente la primera serie femenina, ampliando el proyecto deportivo a niñas y jóvenes de la comuna.</t>
+  </si>
+  <si>
+    <t>2023</t>
+  </si>
+  <si>
+    <t>Ascenso a Primera A comunal</t>
+  </si>
+  <si>
+    <t>El plantel adulto asciende a la máxima categoría de la liga comunal tras una campaña invicta como local.</t>
+  </si>
+  <si>
+    <t>Rojo, Azul, Blanco</t>
+  </si>
+  <si>
+    <t>1961</t>
+  </si>
+  <si>
+    <t>Un grupo de vecinos funda el club en torno a una cancha de tierra, con el objetivo de darle un espacio de encuentro a la comunidad.</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -47,81 +155,23 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+  <cellXfs count="2">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -409,104 +459,70 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:H2"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col width="36" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="11" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="33" customWidth="1" min="7" max="7"/>
-    <col width="45" customWidth="1" min="8" max="8"/>
+    <col min="1" max="1" width="36" customWidth="1"/>
+    <col min="2" max="2" width="18" customWidth="1"/>
+    <col min="3" max="3" width="11" customWidth="1"/>
+    <col min="4" max="4" width="12" customWidth="1"/>
+    <col min="5" max="5" width="15" customWidth="1"/>
+    <col min="6" max="6" width="14" customWidth="1"/>
+    <col min="7" max="7" width="33" customWidth="1"/>
+    <col min="8" max="8" width="45" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>nombre</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>apodo</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>fundacion</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>comuna</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>region</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>colores</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>estadio</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>resumen</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Club Deportivo Juventud San Rafael</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>J con U, La Juve</t>
-        </is>
-      </c>
-      <c r="C2" t="n">
-        <v>1962</v>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>La Pintana</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Rojo, Blanco</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>Estadio Municipal de La Pintana</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>Fundado por un grupo de vecinos de San Rafael, el club nació como espacio de encuentro y hoy reúne a más de 300 jugadoras y jugadores en sus distintas series, desde Escuela de Fútbol hasta el plantel adulto.</t>
-        </is>
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2">
+        <v>1961</v>
+      </c>
+      <c r="D2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F2" t="s">
+        <v>30</v>
+      </c>
+      <c r="G2" t="s">
+        <v>12</v>
+      </c>
+      <c r="H2" t="s">
+        <v>13</v>
       </c>
     </row>
   </sheetData>
@@ -515,119 +531,79 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:C6"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="29" customWidth="1" min="2" max="2"/>
-    <col width="45" customWidth="1" min="3" max="3"/>
+    <col min="1" max="1" width="10" style="1" customWidth="1"/>
+    <col min="2" max="2" width="29" customWidth="1"/>
+    <col min="3" max="3" width="45" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>anio</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>titulo</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>texto</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>1962</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Fundación</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Un grupo de vecinos funda el club en torno a una cancha de tierra, con el objetivo de darle un espacio de encuentro a la comunidad ferroviaria.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>1978</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Primer título comunal</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>El primer equipo se corona campeón de la liga vecinal, el primer trofeo que se exhibe en la sede social.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>1991</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Construcción de la sede</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Con trabajo comunitario y aportes de socios se levanta la sede social, que hasta hoy funciona como punto de encuentro de las familias del club.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>2005</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Nace la rama femenina</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Se forma oficialmente la primera serie femenina, ampliando el proyecto deportivo a niñas y jóvenes de la comuna.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Ascenso a Primera A comunal</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>El plantel adulto asciende a la máxima categoría de la liga comunal tras una campaña invicta como local.</t>
-        </is>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C2" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C5" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B6" t="s">
+        <v>28</v>
+      </c>
+      <c r="C6" t="s">
+        <v>29</v>
       </c>
     </row>
   </sheetData>

--- a/data/club.xlsx
+++ b/data/club.xlsx
@@ -1,143 +1,34 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\marce\Proyectos\juventud-san-rafael\data\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7504A343-B022-4504-87FD-627F3D8BA15B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Club" sheetId="1" r:id="rId1"/>
-    <sheet name="Hitos" sheetId="2" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Club" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Hitos" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <definedNames/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="33">
-  <si>
-    <t>nombre</t>
-  </si>
-  <si>
-    <t>apodo</t>
-  </si>
-  <si>
-    <t>fundacion</t>
-  </si>
-  <si>
-    <t>comuna</t>
-  </si>
-  <si>
-    <t>region</t>
-  </si>
-  <si>
-    <t>colores</t>
-  </si>
-  <si>
-    <t>estadio</t>
-  </si>
-  <si>
-    <t>resumen</t>
-  </si>
-  <si>
-    <t>Club Deportivo Juventud San Rafael</t>
-  </si>
-  <si>
-    <t>J con U, La Juve</t>
-  </si>
-  <si>
-    <t>La Pintana</t>
-  </si>
-  <si>
-    <t>Metropolitana</t>
-  </si>
-  <si>
-    <t>Estadio Municipal de La Pintana</t>
-  </si>
-  <si>
-    <t>Fundado por un grupo de vecinos de San Rafael, el club nació como espacio de encuentro y hoy reúne a más de 300 jugadoras y jugadores en sus distintas series, desde Escuela de Fútbol hasta el plantel adulto.</t>
-  </si>
-  <si>
-    <t>anio</t>
-  </si>
-  <si>
-    <t>titulo</t>
-  </si>
-  <si>
-    <t>texto</t>
-  </si>
-  <si>
-    <t>Fundación</t>
-  </si>
-  <si>
-    <t>1978</t>
-  </si>
-  <si>
-    <t>Primer título comunal</t>
-  </si>
-  <si>
-    <t>El primer equipo se corona campeón de la liga vecinal, el primer trofeo que se exhibe en la sede social.</t>
-  </si>
-  <si>
-    <t>1991</t>
-  </si>
-  <si>
-    <t>Construcción de la sede</t>
-  </si>
-  <si>
-    <t>Con trabajo comunitario y aportes de socios se levanta la sede social, que hasta hoy funciona como punto de encuentro de las familias del club.</t>
-  </si>
-  <si>
-    <t>2005</t>
-  </si>
-  <si>
-    <t>Nace la rama femenina</t>
-  </si>
-  <si>
-    <t>Se forma oficialmente la primera serie femenina, ampliando el proyecto deportivo a niñas y jóvenes de la comuna.</t>
-  </si>
-  <si>
-    <t>2023</t>
-  </si>
-  <si>
-    <t>Ascenso a Primera A comunal</t>
-  </si>
-  <si>
-    <t>El plantel adulto asciende a la máxima categoría de la liga comunal tras una campaña invicta como local.</t>
-  </si>
-  <si>
-    <t>Rojo, Azul, Blanco</t>
-  </si>
-  <si>
-    <t>1961</t>
-  </si>
-  <si>
-    <t>Un grupo de vecinos funda el club en torno a una cancha de tierra, con el objetivo de darle un espacio de encuentro a la comunidad.</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="1">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -156,22 +47,81 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -459,70 +409,137 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H2"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="36" customWidth="1"/>
-    <col min="2" max="2" width="18" customWidth="1"/>
-    <col min="3" max="3" width="11" customWidth="1"/>
-    <col min="4" max="4" width="12" customWidth="1"/>
-    <col min="5" max="5" width="15" customWidth="1"/>
-    <col min="6" max="6" width="14" customWidth="1"/>
-    <col min="7" max="7" width="33" customWidth="1"/>
-    <col min="8" max="8" width="45" customWidth="1"/>
+    <col width="36" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="33" customWidth="1" min="7" max="7"/>
+    <col width="45" customWidth="1" min="8" max="8"/>
+    <col width="41" customWidth="1" min="9" max="9"/>
+    <col width="40" customWidth="1" min="10" max="10"/>
+    <col width="27" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C2">
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>nombre</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>apodo</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>fundacion</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>comuna</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>region</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>colores</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>estadio</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>resumen</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>instagram</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>facebook</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>whatsapp</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Club Deportivo Juventud San Rafael</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>J con U, La Juve</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
         <v>1961</v>
       </c>
-      <c r="D2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F2" t="s">
-        <v>30</v>
-      </c>
-      <c r="G2" t="s">
-        <v>12</v>
-      </c>
-      <c r="H2" t="s">
-        <v>13</v>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>La Pintana</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Rojo, Azul, Blanco</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Estadio Municipal de La Pintana</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Fundado por un grupo de vecinos de San Rafael, el club nació como espacio de encuentro y hoy reúne a más de 300 jugadoras y jugadores en sus distintas series, desde Escuela de Fútbol hasta el plantel adulto.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>https://instagram.com/juventudsanrafael</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>https://facebook.com/juventudsanrafael</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>https://wa.me/56900000000</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -531,79 +548,119 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:C6"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="10" style="1" customWidth="1"/>
-    <col min="2" max="2" width="29" customWidth="1"/>
-    <col min="3" max="3" width="45" customWidth="1"/>
+    <col width="10" customWidth="1" style="1" min="1" max="1"/>
+    <col width="29" customWidth="1" min="2" max="2"/>
+    <col width="45" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B1" t="s">
-        <v>15</v>
-      </c>
-      <c r="C1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A2" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="B2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C2" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="B3" t="s">
-        <v>19</v>
-      </c>
-      <c r="C3" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A4" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="B4" t="s">
-        <v>22</v>
-      </c>
-      <c r="C4" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A5" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="B5" t="s">
-        <v>25</v>
-      </c>
-      <c r="C5" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A6" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="B6" t="s">
-        <v>28</v>
-      </c>
-      <c r="C6" t="s">
-        <v>29</v>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>anio</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>titulo</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>texto</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>1961</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Fundación</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Un grupo de vecinos funda el club en torno a una cancha de tierra, con el objetivo de darle un espacio de encuentro a la comunidad.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>1978</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Primer título comunal</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>El primer equipo se corona campeón de la liga vecinal, el primer trofeo que se exhibe en la sede social.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>1991</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Construcción de la sede</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Con trabajo comunitario y aportes de socios se levanta la sede social, que hasta hoy funciona como punto de encuentro de las familias del club.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>2005</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Nace la rama femenina</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Se forma oficialmente la primera serie femenina, ampliando el proyecto deportivo a niñas y jóvenes de la comuna.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Ascenso a Primera A comunal</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>El plantel adulto asciende a la máxima categoría de la liga comunal tras una campaña invicta como local.</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/data/club.xlsx
+++ b/data/club.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\marce\Proyectos\juventud-san-rafael\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2FB9DA55-40D7-4C38-AAC1-A9D78BC96D32}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{614DBFA1-0D7C-4626-8DCE-CD01F5B3E95D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Club" sheetId="1" r:id="rId1"/>
@@ -62,9 +62,6 @@
     <t>J con U, La Juve</t>
   </si>
   <si>
-    <t>La Pintana</t>
-  </si>
-  <si>
     <t>Metropolitana</t>
   </si>
   <si>
@@ -138,6 +135,9 @@
   </si>
   <si>
     <t>Estadio Municipal de La Pintana, Complejo Deportivo Las Rosas</t>
+  </si>
+  <si>
+    <t>Rey Don Felipe 1330 La Pintana</t>
   </si>
 </sst>
 </file>
@@ -551,28 +551,28 @@
         <v>1961</v>
       </c>
       <c r="D2" t="s">
+        <v>38</v>
+      </c>
+      <c r="E2" t="s">
         <v>13</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>14</v>
       </c>
-      <c r="F2" t="s">
+      <c r="G2" t="s">
+        <v>37</v>
+      </c>
+      <c r="H2" t="s">
         <v>15</v>
       </c>
-      <c r="G2" t="s">
-        <v>38</v>
-      </c>
-      <c r="H2" t="s">
-        <v>16</v>
-      </c>
       <c r="I2" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="J2" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="J2" s="2" t="s">
+      <c r="K2" s="2" t="s">
         <v>22</v>
-      </c>
-      <c r="K2" s="2" t="s">
-        <v>23</v>
       </c>
     </row>
   </sheetData>
@@ -597,68 +597,68 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B1" t="s">
         <v>17</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>18</v>
-      </c>
-      <c r="C1" t="s">
-        <v>19</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C2" t="s">
         <v>24</v>
-      </c>
-      <c r="C2" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B3" t="s">
         <v>26</v>
       </c>
-      <c r="B3" t="s">
+      <c r="C3" t="s">
         <v>27</v>
-      </c>
-      <c r="C3" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B4" t="s">
+        <v>31</v>
+      </c>
+      <c r="C4" t="s">
         <v>32</v>
-      </c>
-      <c r="C4" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B6" t="s">
+        <v>35</v>
+      </c>
+      <c r="C6" t="s">
         <v>36</v>
-      </c>
-      <c r="C6" t="s">
-        <v>37</v>
       </c>
     </row>
   </sheetData>

--- a/data/club.xlsx
+++ b/data/club.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\marce\Proyectos\juventud-san-rafael\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{614DBFA1-0D7C-4626-8DCE-CD01F5B3E95D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9812CAA1-CB0B-4A1D-A7D2-D0800D0AECFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -134,10 +134,10 @@
     <t>Lanzamiento oficial de la campaña "No más violencia en las canchas". Ante el aumento de la delincuencia y los roces en el fútbol amateur de Santiago, Juventud San Rafael se convierte en un referente comunal al liderar iniciativas de convivencia escolar y deportiva. El club reafirma su rol como "escuela formativa", priorizando los valores, la disciplina y la vida sana por sobre los resultados en el marcador.</t>
   </si>
   <si>
-    <t>Estadio Municipal de La Pintana, Complejo Deportivo Las Rosas</t>
-  </si>
-  <si>
-    <t>Rey Don Felipe 1330 La Pintana</t>
+    <t>Estadio Municipal de La Pintana, Complejo Deportivo Las Rosas, Estadio Rául del Canto</t>
+  </si>
+  <si>
+    <t>Rey Don Felipe 1330, La Pintana</t>
   </si>
 </sst>
 </file>

--- a/data/club.xlsx
+++ b/data/club.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\marce\Proyectos\juventud-san-rafael\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9812CAA1-CB0B-4A1D-A7D2-D0800D0AECFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BEC14493-F8E3-4C1A-8542-E8FC7D50EB4D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -86,9 +86,6 @@
     <t>https://instagram.com/club_juventudsanrafael</t>
   </si>
   <si>
-    <t>https://facebook.com/clubjuventudsanrafael</t>
-  </si>
-  <si>
     <t>https://wa.me/56950172752</t>
   </si>
   <si>
@@ -138,6 +135,9 @@
   </si>
   <si>
     <t>Rey Don Felipe 1330, La Pintana</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/clubjuventudsnrafael</t>
   </si>
 </sst>
 </file>
@@ -551,7 +551,7 @@
         <v>1961</v>
       </c>
       <c r="D2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E2" t="s">
         <v>13</v>
@@ -560,7 +560,7 @@
         <v>14</v>
       </c>
       <c r="G2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="H2" t="s">
         <v>15</v>
@@ -569,10 +569,10 @@
         <v>20</v>
       </c>
       <c r="J2" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="K2" s="2" t="s">
         <v>21</v>
-      </c>
-      <c r="K2" s="2" t="s">
-        <v>22</v>
       </c>
     </row>
   </sheetData>
@@ -611,54 +611,54 @@
         <v>19</v>
       </c>
       <c r="B2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C2" t="s">
         <v>23</v>
-      </c>
-      <c r="C2" t="s">
-        <v>24</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B3" t="s">
         <v>25</v>
       </c>
-      <c r="B3" t="s">
+      <c r="C3" t="s">
         <v>26</v>
-      </c>
-      <c r="C3" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B4" t="s">
+        <v>30</v>
+      </c>
+      <c r="C4" t="s">
         <v>31</v>
-      </c>
-      <c r="C4" t="s">
-        <v>32</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B6" t="s">
+        <v>34</v>
+      </c>
+      <c r="C6" t="s">
         <v>35</v>
-      </c>
-      <c r="C6" t="s">
-        <v>36</v>
       </c>
     </row>
   </sheetData>
